--- a/reports/pdf_rolling5_20261012.xlsx
+++ b/reports/pdf_rolling5_20261012.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,326억   ·   현금 23억(0.4%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 8종목  /  매도 24종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,364억   ·   현금 12억(0.2%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 8종목  /  매도 24종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>301</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4857371163</v>
+        <v>4852419713</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-219</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2487834961</v>
+        <v>-2485298941</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>154</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>13279401080</v>
+        <v>13265864480</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-73</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2395454215</v>
+        <v>-2393012365</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>96</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5433953760</v>
+        <v>5428414560</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-66</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-942701510</v>
+        <v>-941740550</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>545514335</v>
+        <v>544958255</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-56</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1576662782</v>
+        <v>-1575055582</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>998559635</v>
+        <v>997541735</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-47</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1657546211</v>
+        <v>-1655856561</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1949442683</v>
+        <v>1947455483</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-46</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1462082012</v>
+        <v>-1460591612</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>496385868</v>
+        <v>495879868</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-28</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2551776524</v>
+        <v>-2549175324</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>526600660</v>
+        <v>526063860</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-28</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-325770394</v>
+        <v>-325438314</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-593406743</v>
+        <v>-1067268717</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.21%→0.00%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>81→58</t>
+          <t>23→0</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1068357767</v>
+        <v>-592801843</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.00%</t>
+          <t>0.38%→0.28%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>23→0</t>
+          <t>81→58</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         <v>-21</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1510052900</v>
+        <v>-1508513600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>-19</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-900263461</v>
+        <v>-899345761</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>-15</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-950588748</v>
+        <v>-949619748</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-84297308</v>
+        <v>-84211378</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-276053327</v>
+        <v>-275771927</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>-11</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-938816751</v>
+        <v>-937859751</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>-8</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-317451516</v>
+        <v>-317127916</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1272,23 +1272,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1654946561</v>
+        <v>-509011865</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.90%→1.37%</t>
+          <t>0.38%→0.34%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>38→31</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1300,23 +1300,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-509531265</v>
+        <v>-1653259561</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.34%</t>
+          <t>1.90%→1.37%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>38→31</t>
         </is>
       </c>
     </row>
@@ -1328,23 +1328,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-540923257</v>
+        <v>-136121964</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.42%</t>
+          <t>0.45%→0.38%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1356,23 +1356,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1233116673</v>
+        <v>-540371857</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>6.65%→7.06%</t>
+          <t>0.49%→0.42%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1384,23 +1384,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-136260864</v>
+        <v>-1231859673</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.38%</t>
+          <t>6.65%→7.06%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-915272757</v>
+        <v>-914339757</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-890257264</v>
+        <v>-889349764</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,467억   ·   현금 53억(1.6%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 8종목  /  매도 7종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,314억   ·   현금 27억(0.8%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1559,7 +1559,7 @@
         <v>122</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1642712136</v>
+        <v>1652063062</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>-258</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2530327932</v>
+        <v>-2544731496</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>119</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1589774972</v>
+        <v>1598824560</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>-233</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-931983938</v>
+        <v>-937289135</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>95</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>2102730559</v>
+        <v>2114700080</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>-122</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-936120889</v>
+        <v>-941449636</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>37</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>935952249</v>
+        <v>941280036</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>-70</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-946228751</v>
+        <v>-951615036</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>337754390</v>
+        <v>339677013</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>-20</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-979166260</v>
+        <v>-984740037</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>13</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>301444080</v>
+        <v>303160011</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>-19</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-297386179</v>
+        <v>-299079011</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>946492251</v>
+        <v>951880036</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>-16</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-989073863</v>
+        <v>-994704038</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>291747278</v>
+        <v>293408011</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,834억   ·   현금 69억(2.4%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 7종목  /  매도 11종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,827억   ·   현금 34억(1.2%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 7종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1984,7 +1984,7 @@
         <v>31</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>1331729441</v>
+        <v>1325721601</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>-195</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1501636997</v>
+        <v>-1494862652</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>21</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2925668468</v>
+        <v>2912469880</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>-96</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1784328590</v>
+        <v>-1776278937</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>20</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>805980267</v>
+        <v>802344242</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>-66</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1143334878</v>
+        <v>-1138176944</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>977816323</v>
+        <v>973405094</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2130,23 +2130,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-874475289</v>
+        <v>-949970287</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.19%</t>
+          <t>0.36%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1249867913</v>
+        <v>1244229376</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2174,23 +2174,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-954275316</v>
+        <v>-870530263</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.00%</t>
+          <t>0.48%→0.19%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>4529981499</v>
+        <v>4509545362</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>-33</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1141140378</v>
+        <v>-1135992343</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>10</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>2068150684</v>
+        <v>2058820622</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>-30</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1322685438</v>
+        <v>-1316718398</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>-28</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-660079218</v>
+        <v>-657101399</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>-26</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1296750429</v>
+        <v>-1290900390</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>-17</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-2724505901</v>
+        <v>-2712214819</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>-10</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-456190151</v>
+        <v>-454132137</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,225억   ·   현금 18억(0.9%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 2종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,114억   ·   현금 9억(0.4%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2493,7 +2493,7 @@
         <v>295</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>4683419752</v>
+        <v>4708199009</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>-342</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-1407815566</v>
+        <v>-1415264102</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>211</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>2121562688</v>
+        <v>2132787551</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>-208</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-2995574242</v>
+        <v>-3011423366</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>-60</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-2106971889</v>
+        <v>-2118119554</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>-45</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-816479957</v>
+        <v>-820799827</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 315억   ·   현금 7억(2.2%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 8종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 321억   ·   현금 4억(1.1%)      오늘 2026-10-12  vs  5일전 2026-10-01      매수 8종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B66" s="4" t="n"/>
@@ -2726,11 +2726,11 @@
         <v>89</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>94411172</v>
+        <v>99555429</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.30%</t>
+          <t>0.00%→0.31%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2747,11 +2747,11 @@
         <v>-260</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-210038338</v>
+        <v>-210745662</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2.11%→1.45%</t>
+          <t>2.07%→1.42%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2770,11 +2770,11 @@
         <v>42</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>14237156</v>
+        <v>13894444</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>2.78%→2.84%</t>
+          <t>2.66%→2.72%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2791,11 +2791,11 @@
         <v>-60</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-58343983</v>
+        <v>-57324017</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>0.68%→0.50%</t>
+          <t>0.66%→0.48%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2814,11 +2814,11 @@
         <v>37</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>61767782</v>
+        <v>64158019</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.36%→2.57%</t>
+          <t>2.40%→2.62%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -2835,11 +2835,11 @@
         <v>-15</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-96593972</v>
+        <v>-88740026</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.03%</t>
+          <t>1.20%→0.93%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -2858,7 +2858,7 @@
         <v>34</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>96410372</v>
+        <v>96872828</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
@@ -2879,11 +2879,11 @@
         <v>-14</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-39031989</v>
+        <v>-39032011</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>2.22%→2.10%</t>
+          <t>2.17%→2.06%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2902,11 +2902,11 @@
         <v>18</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>31823991</v>
+        <v>31640409</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>4.70%→4.83%</t>
+          <t>4.58%→4.71%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -2923,11 +2923,11 @@
         <v>-12</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-39779988</v>
+        <v>-46756814</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.96%</t>
+          <t>1.24%→1.10%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -2946,11 +2946,11 @@
         <v>16</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>40854388</v>
+        <v>38569611</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>1.16%→1.30%</t>
+          <t>1.07%→1.20%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
@@ -2967,11 +2967,11 @@
         <v>-11</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-81606776</v>
+        <v>-93724428</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>2.27%→2.03%</t>
+          <t>2.56%→2.28%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -2983,23 +2983,23 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>46647986</v>
+        <v>81940024</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>2.56%→2.73%</t>
+          <t>0.97%→1.24%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -3011,11 +3011,11 @@
         <v>-7</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-30701991</v>
+        <v>-31939609</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.72%</t>
+          <t>2.86%→2.77%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3027,23 +3027,23 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>87379974</v>
+        <v>49334015</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.35%</t>
+          <t>2.66%→2.83%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -3055,11 +3055,11 @@
         <v>-5</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-69359980</v>
+        <v>-71230021</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>3.28%→3.07%</t>
+          <t>3.30%→3.09%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3083,11 +3083,11 @@
         <v>-3</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-33272390</v>
+        <v>-33496810</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2.55%→2.46%</t>
+          <t>2.52%→2.43%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3116,7 +3116,7 @@
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      오늘 2026-10-12  vs  5일전 2026-10-01      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,157억      오늘 2026-10-12  vs  5일전 2026-10-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B81" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261012.xlsx
+++ b/reports/pdf_rolling5_20261012.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1067268717</v>
+        <v>-592801843</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.00%</t>
+          <t>0.38%→0.28%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>23→0</t>
+          <t>81→58</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-592801843</v>
+        <v>-1067268717</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.21%→0.00%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>81→58</t>
+          <t>23→0</t>
         </is>
       </c>
     </row>
@@ -1328,23 +1328,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-136121964</v>
+        <v>-540371857</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.38%</t>
+          <t>0.49%→0.42%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1356,23 +1356,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-540371857</v>
+        <v>-1231859673</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.42%</t>
+          <t>6.65%→7.06%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1384,23 +1384,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1231859673</v>
+        <v>-136121964</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>6.65%→7.06%</t>
+          <t>0.45%→0.38%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1412,23 +1412,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-914339757</v>
+        <v>-889349764</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.72%→2.56%</t>
+          <t>0.91%→0.66%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -1440,23 +1440,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-889349764</v>
+        <v>-914339757</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.66%</t>
+          <t>2.72%→2.56%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -2130,23 +2130,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-949970287</v>
+        <v>-870530263</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.00%</t>
+          <t>0.48%→0.19%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2174,23 +2174,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-870530263</v>
+        <v>-949970287</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.19%</t>
+          <t>0.36%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261012.xlsx
+++ b/reports/pdf_rolling5_20261012.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-592801843</v>
+        <v>-1067268717</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.21%→0.00%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>81→58</t>
+          <t>23→0</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1067268717</v>
+        <v>-592801843</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.00%</t>
+          <t>0.38%→0.28%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>23→0</t>
+          <t>81→58</t>
         </is>
       </c>
     </row>
@@ -1272,23 +1272,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-509011865</v>
+        <v>-1653259561</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.34%</t>
+          <t>1.90%→1.37%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>38→31</t>
         </is>
       </c>
     </row>
@@ -1300,23 +1300,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1653259561</v>
+        <v>-509011865</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.90%→1.37%</t>
+          <t>0.38%→0.34%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>38→31</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1412,23 +1412,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-889349764</v>
+        <v>-914339757</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.66%</t>
+          <t>2.72%→2.56%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -1440,23 +1440,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-914339757</v>
+        <v>-889349764</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.72%→2.56%</t>
+          <t>0.91%→0.66%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -2130,23 +2130,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-870530263</v>
+        <v>-949970287</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.19%</t>
+          <t>0.36%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2174,23 +2174,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-949970287</v>
+        <v>-870530263</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.00%</t>
+          <t>0.48%→0.19%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2983,23 +2983,23 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>81940024</v>
+        <v>49334015</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.24%</t>
+          <t>2.66%→2.83%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -3027,23 +3027,23 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>49334015</v>
+        <v>81940024</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.83%</t>
+          <t>0.97%→1.24%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261012.xlsx
+++ b/reports/pdf_rolling5_20261012.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1067268717</v>
+        <v>-592801843</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.00%</t>
+          <t>0.38%→0.28%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>23→0</t>
+          <t>81→58</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-592801843</v>
+        <v>-1067268717</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.21%→0.00%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>81→58</t>
+          <t>23→0</t>
         </is>
       </c>
     </row>
@@ -1272,23 +1272,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1653259561</v>
+        <v>-509011865</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.90%→1.37%</t>
+          <t>0.38%→0.34%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>38→31</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1300,23 +1300,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-509011865</v>
+        <v>-1653259561</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.34%</t>
+          <t>1.90%→1.37%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>38→31</t>
         </is>
       </c>
     </row>
@@ -1328,23 +1328,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-540371857</v>
+        <v>-1231859673</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.42%</t>
+          <t>6.65%→7.06%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1356,23 +1356,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1231859673</v>
+        <v>-136121964</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>6.65%→7.06%</t>
+          <t>0.45%→0.38%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1384,23 +1384,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-136121964</v>
+        <v>-540371857</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.38%</t>
+          <t>0.49%→0.42%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1412,23 +1412,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-914339757</v>
+        <v>-889349764</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.72%→2.56%</t>
+          <t>0.91%→0.66%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -1440,23 +1440,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-889349764</v>
+        <v>-914339757</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.66%</t>
+          <t>2.72%→2.56%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -2130,23 +2130,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-949970287</v>
+        <v>-870530263</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.00%</t>
+          <t>0.48%→0.19%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2174,23 +2174,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-870530263</v>
+        <v>-949970287</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.19%</t>
+          <t>0.36%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
